--- a/Results/Feature-importance.xlsx
+++ b/Results/Feature-importance.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08708473353808953</v>
+        <v>0.08579295618790697</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04985507714330342</v>
+        <v>0.04974587512071572</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -481,10 +481,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03718899750523563</v>
+        <v>0.04551001085132624</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1103225767973287</v>
+        <v>0.1100253035217236</v>
       </c>
       <c r="D4" t="inlineStr"/>
     </row>
@@ -495,13 +495,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03586561387020661</v>
+        <v>0.03897504684876754</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04226614877181136</v>
+        <v>0.0434991650714077</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04657364719734827</v>
+        <v>0.04827227854653553</v>
       </c>
     </row>
     <row r="6">
@@ -511,72 +511,72 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02006282269753548</v>
+        <v>0.02062280771018849</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03078147309071343</v>
+        <v>0.03105269040860733</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03775837351274001</v>
+        <v>0.03875941069630109</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Walking</t>
+          <t>Blood pressure</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01871159285322398</v>
+        <v>0.01850819407327014</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03459657241588492</v>
+        <v>0.02431518365282673</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0528365521049821</v>
+        <v>0.02596350766883215</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Blood pressure</t>
+          <t>Walking</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01700761421073044</v>
+        <v>0.01843038786422963</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02407304387311195</v>
+        <v>0.03415597736282613</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02536497931888568</v>
+        <v>0.05291823223764078</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Probable Depression</t>
+          <t>Psychosocial functioning</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01047707822502877</v>
+        <v>0.01202156355088393</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01304294316643053</v>
+        <v>0.01268250813740661</v>
       </c>
       <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Psychosocial functioning</t>
+          <t>Probable Depression</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.009201542608678281</v>
+        <v>0.01081312757359014</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0107384409025132</v>
+        <v>0.01332561767120497</v>
       </c>
       <c r="D10" t="inlineStr"/>
     </row>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.008353798156601189</v>
+        <v>0.008744517720745745</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01830819160886183</v>
+        <v>0.01816406347125096</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0512374715705919</v>
+        <v>0.05234576858480581</v>
       </c>
     </row>
     <row r="12">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.005226147872171462</v>
+        <v>0.006353281786197274</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -615,27 +615,29 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.00449984238398174</v>
+        <v>0.004210565003993172</v>
       </c>
       <c r="C13" t="n">
-        <v>0.008978402756189522</v>
+        <v>0.008867295082045982</v>
       </c>
       <c r="D13" t="n">
-        <v>0.009956469100172343</v>
+        <v>0.01024301774981158</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Physical activity increase</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.003207079061665034</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+        <v>0.003762266752900483</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.02760461483244332</v>
+      </c>
       <c r="D14" t="n">
-        <v>0.004923962712509148</v>
+        <v>0.02625074027382705</v>
       </c>
     </row>
     <row r="15">
@@ -645,29 +647,27 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.003176760115654475</v>
+        <v>0.003369902200212438</v>
       </c>
       <c r="C15" t="n">
-        <v>0.008493705294127176</v>
+        <v>0.008485866732690223</v>
       </c>
       <c r="D15" t="n">
-        <v>0.008895720308783018</v>
+        <v>0.009470014734771836</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Heart disease</t>
+          <t>Physical activity increase</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.003123507911594645</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.003823734054265082</v>
-      </c>
+        <v>0.003340344327394476</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.004643530978259697</v>
+        <v>0.005203863087625883</v>
       </c>
     </row>
     <row r="17">
@@ -677,103 +677,99 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.002716191401704172</v>
+        <v>0.00280148953876063</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0009801887657370442</v>
+        <v>0.001173576121816883</v>
       </c>
       <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Pain</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.002479204792279321</v>
+        <v>0.002481871818334736</v>
       </c>
       <c r="C18" t="n">
-        <v>0.02766592733436014</v>
+        <v>0.009542679376125855</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02624565120391486</v>
+        <v>0.00788569684243489</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Visual impairment</t>
+          <t>Angina</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.002323085224397949</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.002247528498078474</v>
-      </c>
+        <v>0.002296909154476084</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.002706761191986505</v>
+        <v>0.0006704031669433986</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Pain</t>
+          <t>Arthritis</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.002083956521211209</v>
+        <v>0.002231365385572789</v>
       </c>
       <c r="C20" t="n">
-        <v>0.009161839087604732</v>
+        <v>0.00185503886423805</v>
       </c>
       <c r="D20" t="n">
-        <v>0.008082133623584153</v>
+        <v>0.002918912347479094</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Arthritis</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.001744173575142831</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
+        <v>0.002007927271265757</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.003700246180762316</v>
+      </c>
       <c r="D21" t="n">
-        <v>0.002235381121754235</v>
+        <v>0.001739588716279471</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>Neuropsychiatric score</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.001480756606576753</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.00360525653878208</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.00165172626198473</v>
-      </c>
+        <v>0.001946744781996606</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Lifetime health burden score</t>
+          <t>Blood pressure ratio</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.001439122518180367</v>
+        <v>0.001729805822016684</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
-        <v>0.0009354428954069172</v>
+        <v>0.004182978271166505</v>
       </c>
     </row>
     <row r="24">
@@ -783,13 +779,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.00122272103439328</v>
+        <v>0.001644006018407158</v>
       </c>
       <c r="C24" t="n">
-        <v>0.002096473226473644</v>
+        <v>0.002155308833957179</v>
       </c>
       <c r="D24" t="n">
-        <v>0.00219842371366332</v>
+        <v>0.002470108256268606</v>
       </c>
     </row>
     <row r="25">
@@ -799,73 +795,77 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.001023581771751746</v>
+        <v>0.001263628043542908</v>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>0.00164004350633076</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Blood pressure ratio</t>
+          <t>Fainting episodes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0008390771827945095</v>
+        <v>0.0006258094186853579</v>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="n">
-        <v>0.003954695774485606</v>
-      </c>
+      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Fainting episodes</t>
+          <t>Gastrointestinal impairment</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0007379688307394266</v>
+        <v>0.0002488445628043301</v>
       </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>0.001106821679395135</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Neuropsychiatric symptom severity</t>
+          <t>Familial Memory Impairment</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0007276678146371536</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+        <v>0.000141990946246597</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0001267986919203057</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.0002928313121877887</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Breathlessness</t>
+          <t>Persistent cough</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0004302941930861737</v>
+        <v>0.000197783248833708</v>
       </c>
       <c r="C29" t="n">
-        <v>0.002294049093323163</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.003006965489264567</v>
-      </c>
+        <v>1.613490144470616e-05</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Depressive episode</t>
+          <t>Mental Distress</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0002745934615843534</v>
+        <v>0.0002012202381848253</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
@@ -873,135 +873,93 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Mental Distress</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0.0001703763880727086</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+          <t>Heart disease</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="n">
+        <v>0.004009554827310807</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.005058427749245921</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Gastrointestinal impairment</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0.0001433101757802761</v>
-      </c>
+          <t>Visual impairment</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>0.001352559178032098</v>
-      </c>
-      <c r="D32" t="inlineStr"/>
+        <v>0.002751780164083117</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.003508290301074525</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Angina</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>0.0001252405687663775</v>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="n">
-        <v>0.0004934540500821638</v>
-      </c>
+          <t>Respiratory burden score</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="n">
+        <v>0.002670876798428422</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Familial Memory Impairment</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>7.60235023749715e-05</v>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>Transient ischemic attack</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="n">
+        <v>0.002116410749063861</v>
+      </c>
       <c r="D34" t="n">
-        <v>2.675610703008442e-05</v>
+        <v>0.001332087050236499</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Respiratory burden score</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>5.413434199833311e-05</v>
-      </c>
+          <t>Illness-related burden</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>0.000297781604511775</v>
+        <v>0.000727911694367923</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0001030669682619382</v>
+        <v>0.0001249068105033087</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>DSM-IV dementia</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>2.86520460733238e-05</v>
-      </c>
+          <t>Breathlessness</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>0.003577367151881354</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Skin-related problems</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>8.378450357082105e-05</v>
-      </c>
+          <t>Lifetime health burden score</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
-        <v>4.479563794390259e-05</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Transient ischemic attack</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="n">
-        <v>0.002234260852892566</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>Persistent cough</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="n">
-        <v>0.0002847262547984267</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.0001452940903846441</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Illness-related burden</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="n">
-        <v>0.0003858098947464846</v>
+        <v>0.001301271997506176</v>
       </c>
     </row>
   </sheetData>
